--- a/static/Upload/FM marks.xlsx
+++ b/static/Upload/FM marks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amit\Documents\GitHub\Mecha\DTU\Aug-Dec 2026\FM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amit\Documents\GitHub\MechanicalCodingThunder.github.io\static\Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934ADD05-A788-414C-B714-DA9E36F0E676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D56C03-1BB9-413B-8905-5C0DD9AD4B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="9766" windowHeight="11363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="129">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
+  <si>
+    <t>Roll No</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Sr No</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Mid Term (20)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -39,7 +60,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -49,7 +70,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -59,7 +80,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -69,7 +90,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -79,7 +100,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -89,7 +110,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -99,7 +120,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -109,7 +130,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -119,7 +140,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -129,7 +150,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -139,7 +160,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -149,7 +170,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -159,7 +180,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -169,7 +190,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -179,7 +200,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -187,9 +208,15 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>25/ME/199</t>
+  </si>
+  <si>
+    <t>PUNEET SHARMA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -199,7 +226,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -209,7 +236,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -219,7 +246,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -229,7 +256,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -239,7 +266,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -249,7 +276,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -259,7 +286,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -269,7 +296,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -279,7 +306,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -289,7 +316,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -299,7 +326,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -309,7 +336,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -319,7 +346,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -329,7 +356,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -339,7 +366,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -349,7 +376,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -359,7 +386,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -369,7 +396,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -379,7 +406,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -389,7 +416,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -399,7 +426,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -409,7 +436,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -419,7 +446,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -429,7 +456,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -439,7 +466,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -449,7 +476,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -459,7 +486,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -469,7 +496,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -479,7 +506,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -489,7 +516,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -499,7 +526,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -509,7 +536,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -519,7 +546,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -529,7 +556,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -539,7 +566,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -549,7 +576,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -559,7 +586,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -569,7 +596,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -579,7 +606,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -589,7 +616,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -599,7 +626,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -609,7 +636,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -619,7 +646,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -629,7 +656,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -639,7 +666,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -649,7 +676,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -659,7 +686,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -669,7 +696,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -679,7 +706,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -689,7 +716,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -699,7 +726,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -709,7 +736,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -719,7 +746,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -729,7 +756,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -739,7 +766,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -749,7 +776,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -759,7 +786,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -769,7 +796,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -779,7 +806,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -789,7 +816,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -799,7 +826,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -809,7 +836,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -819,7 +846,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -829,7 +856,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -839,7 +866,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -849,7 +876,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -859,7 +886,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -869,7 +896,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -879,7 +906,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -889,7 +916,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -899,7 +926,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -909,7 +936,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -919,7 +946,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -929,7 +956,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -939,7 +966,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -949,7 +976,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -959,7 +986,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -969,7 +996,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -979,7 +1006,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -989,7 +1016,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -999,7 +1026,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1009,7 +1036,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1019,7 +1046,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1029,7 +1056,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1039,7 +1066,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1049,7 +1076,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1059,7 +1086,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1069,7 +1096,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1079,7 +1106,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1089,7 +1116,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1099,7 +1126,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1109,7 +1136,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1119,7 +1146,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1129,7 +1156,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1139,7 +1166,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1149,7 +1176,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1159,7 +1186,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1169,7 +1196,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1179,7 +1206,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1189,7 +1216,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1199,7 +1226,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1209,7 +1236,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1219,7 +1246,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1229,7 +1256,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1239,7 +1266,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -1247,32 +1274,14 @@
     </r>
   </si>
   <si>
-    <t>Roll No</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Sr No</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Mid Term (20)</t>
+    <t>AB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1281,12 +1290,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -1325,7 +1340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1333,6 +1348,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1614,718 +1632,915 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultColWidth="13.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.46484375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.796875" style="2" customWidth="1"/>
     <col min="4" max="16384" width="13.06640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>125</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+      <c r="G7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="G8" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="G9" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+      <c r="G10" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="G11" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="G12" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="G13" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="G14" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+      <c r="G15" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="G16" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+      <c r="G17" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+      <c r="G18" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+        <v>42</v>
+      </c>
+      <c r="G19" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+      <c r="G20" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+        <v>46</v>
+      </c>
+      <c r="G21" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+      <c r="G22" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="G23" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+      <c r="G24" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+      <c r="G25" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+        <v>56</v>
+      </c>
+      <c r="G26" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+      <c r="G27" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="G28" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="G29" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="G30" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+      <c r="G31" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+      <c r="G32" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+        <v>69</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+      <c r="G35" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+      <c r="G36" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+        <v>77</v>
+      </c>
+      <c r="G37" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+      <c r="G38" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+      <c r="G39" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+      <c r="G40" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+      <c r="G41" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+      <c r="G42" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+        <v>89</v>
+      </c>
+      <c r="G43" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+      <c r="G44" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+        <v>93</v>
+      </c>
+      <c r="G45" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+      <c r="G46" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+        <v>97</v>
+      </c>
+      <c r="G47" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="G48" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+      <c r="G49" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+      <c r="G50" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+        <v>105</v>
+      </c>
+      <c r="G51" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+      <c r="G52" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+      <c r="G53" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+      <c r="G54" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+      <c r="G55" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="G56" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+      <c r="G57" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+        <v>119</v>
+      </c>
+      <c r="G58" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+        <v>121</v>
+      </c>
+      <c r="G59" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+      <c r="G60" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+      <c r="G61" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="G62" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
+      </c>
+      <c r="G63" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="B64" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G64" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
